--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-03_leave_types_休暇種別_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-03_leave_types_休暇種別_テーブル詳細設計書.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち leave_types を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.2 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
 章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
         </is>
       </c>
@@ -754,8 +754,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>初期 11 件は schema.sql の INSERT（KF-DD-003 総覧の「初期データ」参照）。下記は ONL-015 による追加登録の例。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>初期 11 件は V1__init_schema.sql の INSERT（KF-DD-003 総覧の「初期データ」参照）。下記は ONL-015 による追加登録の例。
+例の INSERT は V1・V2 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>schema.sql 末尾の 11 件（法定休暇）。本番では seed ファイルに分離（課題 C-3）。</t>
+          <t>V1__init_schema.sql 末尾の 11 件（法定休暇）。本番にもそのまま適用される（V1 に含む。休暇種別の追加・変更は ONL-015 または V3 以降のマイグレーションで行い、V1 は編集しない）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1・V2（祝日の初期データ）は適用後に編集せず、列追加・索引追加は次の版 V3__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -1494,94 +1494,94 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="77.5" customHeight="1">
+    <row r="12" ht="48.5" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>C-3</t>
+          <t>C-4</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
+          <t>PK 制約名が未指定で命名規約と不統一</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
+          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
+          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
+          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="77.5" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>C-5</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>業務ルールの CHECK 制約が少ない</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
           <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48.5" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>C-4</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>PK 制約名が未指定で命名規約と不統一</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
     </row>
     <row r="14" ht="77.5" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>C-5</t>
+          <t>C-6</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>業務ルールの CHECK 制約が少ない</t>
+          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1590,30 +1590,30 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15" ht="48.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>C-6</t>
+          <t>LT-1</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
+          <t>leave_types.max_days_rule が NULL 可</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>列は NULL 許可で ck_lt_rule も NULL を通す（SQL の CHECK は NULL で真）。KF-BD-005 と ONL-015 では必須（LIMITED / UNLIMITED）。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
+          <t>NULL の種別は LIMITED でも UNLIMITED でもなく、ONL-005 の残日数判定が不定になる。</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
+          <t>NOT NULL 化（既存 11 件は設定済み）。</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1622,30 +1622,30 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="48.5" customHeight="1">
+    <row r="16" ht="63" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>LT-1</t>
+          <t>LT-2</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>leave_types.max_days_rule が NULL 可</t>
+          <t>年次有給休暇を名称で特定している</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>列は NULL 許可で ck_lt_rule も NULL を通す（SQL の CHECK は NULL で真）。KF-BD-005 と ONL-015 では必須（LIMITED / UNLIMITED）。</t>
+          <t>ONL-013 は findByName('年次有給休暇') で年休を判定。名称変更は ONL-015 が E-016 で拒否するが DB は保護しない。表示順の列も無く id 昇順（ONL-021）。</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>NULL の種別は LIMITED でも UNLIMITED でもなく、ONL-005 の残日数判定が不定になる。</t>
+          <t>SQL 等で改名すると年休判定・年 5 日義務・BAT-001/002 が働かなくなる。</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>NOT NULL 化（既存 11 件は設定済み）。</t>
+          <t>code 列（例 ANNUAL_LEAVE）追加、または name 変更を禁止するトリガ。display_order 列の追加を検討。</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1657,130 +1657,130 @@
     <row r="17" ht="63" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>LT-2</t>
+          <t>LT-3</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>年次有給休暇を名称で特定している</t>
+          <t>日数上限（子の看護・介護休暇、介護休業）は leave_balances の付与で管理</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ONL-013 は findByName('年次有給休暇') で年休を判定。名称変更は ONL-015 が E-016 で拒否するが DB は保護しない。表示順の列も無く id 昇順（ONL-021）。</t>
+          <t>leave_types には上限日数を持たず、LIMITED 種別は管理者の付与（ONL-017）が無いと残 0 日になる。BAT-001 が自動付与するのは年次有給休暇のみ。</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>SQL 等で改名すると年休判定・年 5 日義務・BAT-001/002 が働かなくなる。</t>
+          <t>付与漏れがあると申請時に E-004（残日数不足）となる。運用ルールが DB から読み取れない。</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>code 列（例 ANNUAL_LEAVE）追加、または name 変更を禁止するトリガ。display_order 列の追加を検討。</t>
+          <t>default_days（既定付与日数）列の追加、または付与運用手順を運用設計書に明記。</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="63" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>LT-3</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>日数上限（子の看護・介護休暇、介護休業）は leave_balances の付与で管理</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>leave_types には上限日数を持たず、LIMITED 種別は管理者の付与（ONL-017）が無いと残 0 日になる。BAT-001 が自動付与するのは年次有給休暇のみ。</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>付与漏れがあると申請時に E-004（残日数不足）となる。運用ルールが DB から読み取れない。</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>default_days（既定付与日数）列の追加、または付与運用手順を運用設計書に明記。</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="106.5" customHeight="1">
+    <row r="21" ht="106.5" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>updated_at が更新時に自動更新されない</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="135.5" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>C-2</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>updated_at が更新時に自動更新されない</t>
+          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1794,25 +1794,25 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="92" customHeight="1">
+    <row r="23" ht="135.5" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>C-2</t>
+          <t>C-3</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -2006,16 +2006,16 @@
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="C31:F31"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -2270,10 +2270,10 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ V2__seed_holidays.sql ＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -2308,7 +2308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2367,6 +2367,29 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V2（祝日の初期データ）追加に伴い、データ例の前提を V1・V2 適用直後に更新。マイグレーション記述を次版 V3 に更新。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2381,7 +2404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F39"/>
+  <dimension ref="A2:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2444,7 +2467,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway の V1__init_schema.sql（backend/src/main/resources/db/migration）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -2564,15 +2587,15 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Entity クラス</t>
+          <t>初期データ</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>com.example.kintaiflow.entity.LeaveType（定数 ANNUAL_LEAVE_NAME）</t>
+          <t>V1__init_schema.sql の INSERT で法定休暇 11 種（年次有給休暇・産前産後休業・生理休暇・育児時間・公民権行使・母性健康管理・育児休業・子の看護等休暇・介護休暇・介護休業）。KF-DD-003『初期データ』参照。</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -2583,12 +2606,12 @@
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Entity クラス</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>repository.LeaveTypeRepository（findById / findAllById / findByName / findByIsActiveTrueOrderByIdAsc）</t>
+          <t>com.example.kintaiflow.entity.LeaveType（定数 ANNUAL_LEAVE_NAME）</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -2596,136 +2619,128 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>repository.LeaveTypeRepository（findById / findAllById / findByName / findByIsActiveTrueOrderByIdAsc）</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>1.2 主な利用処理（オンライン処理・バッチ）</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>処理ID</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>処理名</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>API / 種別</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>備考（規格 tables の注記ほか）</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>申請作成</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>API-005 POST /api/requests</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="10" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>申請作成</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>API-005 POST /api/requests</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>ONL-006</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>申請一覧取得</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>API-006 GET /api/requests</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>（種別名の取得）</t>
         </is>
       </c>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>ONL-007</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>申請詳細取得</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>API-007 GET /api/requests/{id}</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>申請詳細取得</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>API-010 POST /api/approvals/{id}/approve</t>
+          <t>API-007 GET /api/requests/{id}</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2733,27 +2748,23 @@
           <t>R</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>（SQL 規格には R あり。tables 記載は なし）</t>
-        </is>
-      </c>
+      <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="10" t="n"/>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>休暇残日数取得</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>API-013 GET /api/leave-balances</t>
+          <t>API-010 POST /api/approvals/{id}/approve</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -2763,7 +2774,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>（年休の種別ID）</t>
+          <t>（SQL 規格には R あり。tables 記載は なし）</t>
         </is>
       </c>
       <c r="F22" s="10" t="n"/>
@@ -2771,46 +2782,50 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-013</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>休暇種別管理</t>
+          <t>休暇残日数取得</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>API-015 GET / POST / PUT /api/admin/leave-types[/{id}]</t>
+          <t>API-013 GET /api/leave-balances</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>C/R/U</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>（年休の種別ID）</t>
+        </is>
+      </c>
       <c r="F23" s="10" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>休暇付与</t>
+          <t>休暇種別管理</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>API-017 GET/POST/PUT /api/admin/leave-grants[/{id}]</t>
+          <t>API-015 GET / POST / PUT /api/admin/leave-types[/{id}]</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C/R/U</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr"/>
@@ -2819,17 +2834,17 @@
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>ONL-021</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>有効休暇種別一覧取得</t>
+          <t>休暇付与</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>API-021 GET /api/leave-types</t>
+          <t>API-017 GET/POST/PUT /api/admin/leave-grants[/{id}]</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -2843,17 +2858,17 @@
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-021</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>申請提出</t>
+          <t>有効休暇種別一覧取得</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>API-022 POST /api/requests/{id}/submit</t>
+          <t>API-021 GET /api/leave-types</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -2864,20 +2879,20 @@
       <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-022</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>申請提出</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>バッチ</t>
+          <t>API-022 POST /api/requests/{id}/submit</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -2891,12 +2906,12 @@
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>年5日取得義務アラート</t>
+          <t>年次有給休暇 自動付与</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -2912,80 +2927,84 @@
       <c r="E28" s="7" t="inlineStr"/>
       <c r="F28" s="10" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>年5日取得義務アラート</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>バッチ</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>バッチ</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>pg_dump による全表読取（アプリ SQL なし）</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>1.3 関連設計書</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>文書番号</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>文書名</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>関連内容</t>
-        </is>
-      </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-003</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>テーブル設計書（総覧）</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>文書番号</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>文書名</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -2995,17 +3014,17 @@
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-003</t>
+          <t>KF-DD-003</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>テーブル定義書（基本）</t>
+          <t>テーブル設計書（総覧）</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>論理名・基本項目</t>
+          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
@@ -3015,17 +3034,17 @@
     <row r="35" ht="19.5" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-005</t>
+          <t>KF-BD-003</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>コード定義書</t>
+          <t>テーブル定義書（基本）</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>コード値と状態遷移の基本設計</t>
+          <t>論理名・基本項目</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
@@ -3035,17 +3054,17 @@
     <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-001</t>
+          <t>KF-BD-005</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>オンライン設計書</t>
+          <t>コード定義書</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>コード値と状態遷移の基本設計</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -3055,17 +3074,17 @@
     <row r="37" ht="19.5" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-ONL-xxx</t>
+          <t>KF-DD-001</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>オンライン詳細設計書</t>
+          <t>オンライン設計書</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>アクセスパターンの根拠（SQL・排他）</t>
+          <t>ONL-001〜022 の概要</t>
         </is>
       </c>
       <c r="D37" s="9" t="n"/>
@@ -3075,17 +3094,17 @@
     <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-004 / BAT</t>
+          <t>KF-DD-ONL-xxx</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>バッチ設計書</t>
+          <t>オンライン詳細設計書</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>BAT-001〜003 の使用</t>
+          <t>アクセスパターンの根拠（SQL・排他）</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
@@ -3095,35 +3114,52 @@
     <row r="39" ht="19.5" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>KF-DD-004 / BAT</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>DDL 本体</t>
+          <t>バッチ設計書</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>BAT-001〜003 の使用</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="10" t="n"/>
     </row>
+    <row r="40" ht="63" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>DDL 本体</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>本書の自動生成元</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
@@ -3131,19 +3167,23 @@
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A31:F31"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="C40:F40"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="E22:F22"/>
@@ -3184,7 +3224,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（V1__init_schema.sql から自動生成）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -3314,7 +3354,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>INSERT 時に DB が自動採番。初期 11 件は schema.sql。</t>
+          <t>INSERT 時に DB が自動採番。初期 11 件は V1__init_schema.sql。</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -3801,7 +3841,7 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は V1__init_schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -3848,7 +3888,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（V1__init_schema.sql の定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -4245,7 +4285,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1・V2＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B22" s="9" t="n"/>
